--- a/csv/policies/reference/Ref_OBPS/formula_Ref_OBPS_SK.xlsx
+++ b/csv/policies/reference/Ref_OBPS/formula_Ref_OBPS_SK.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -527,12 +527,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
